--- a/results/cross_domain_tables.xlsx
+++ b/results/cross_domain_tables.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.4025638759884939</v>
+        <v/>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.4026005690798778</v>
+        <v/>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.6767603191312457</v>
+        <v/>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.3976371924804952</v>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -513,16 +513,16 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.2637911557068653</v>
+        <v/>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.2882269899047988</v>
+        <v/>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.6767603191312457</v>
+        <v/>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.249120011239413</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -600,16 +600,16 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.243858494503865</v>
+        <v>0.2500641673920391</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>0.2451981123308191</v>
+        <v>0.2515401381516011</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6672121804964631</v>
+        <v>0.6707876168449877</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.2283655010405759</v>
+        <v>0.2289135526896438</v>
       </c>
     </row>
     <row r="9">
@@ -629,16 +629,16 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.3050685328306439</v>
+        <v>0.2981713599095536</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>0.3055657990664031</v>
+        <v>0.2982240527109196</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.6671817333152746</v>
+        <v>0.6707900070953513</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.2945427341601534</v>
+        <v>0.2856726759205903</v>
       </c>
     </row>
     <row r="11">
@@ -658,16 +658,16 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.3155247554601252</v>
+        <v/>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0.3154459504258927</v>
+        <v/>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.6982631321230246</v>
+        <v/>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.3070479089818113</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -687,16 +687,16 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.2814671838726204</v>
+        <v/>
       </c>
       <c r="E12" s="1" t="n">
-        <v>0.284386291687972</v>
+        <v/>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.6982631321230246</v>
+        <v/>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.245412910407159</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.1898924934926938</v>
+        <v>0.1947559750686548</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>0.1898004150935746</v>
+        <v>0.1947668482950426</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.6986484810570429</v>
+        <v>0.6992969524073541</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.1920734729070102</v>
+        <v>0.1945305765949548</v>
       </c>
     </row>
     <row r="16">
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.1652858022933041</v>
+        <v>0.1744747700828203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>0.1646402350187151</v>
+        <v>0.1741804085316647</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.6984113158784716</v>
+        <v>0.6991239613359256</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.1825943477557938</v>
+        <v>0.187442247783798</v>
       </c>
     </row>
     <row r="19">
@@ -876,16 +876,16 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.4064339953739314</v>
+        <v/>
       </c>
       <c r="E22" s="1" t="n">
-        <v>0.4063225777461542</v>
+        <v/>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.6368295918022082</v>
+        <v/>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.4075720636728296</v>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -905,16 +905,16 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.2396460790431119</v>
+        <v/>
       </c>
       <c r="E23" s="1" t="n">
-        <v>0.2733410607923364</v>
+        <v/>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.6368295918022082</v>
+        <v/>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.2522474294739795</v>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -992,16 +992,16 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.2284795627070928</v>
+        <v>0.2419269448653047</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>0.2301439524467525</v>
+        <v>0.2428852375284022</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.6285068898100035</v>
+        <v>0.6238543146407811</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.2370181695006364</v>
+        <v>0.24136291383083</v>
       </c>
     </row>
     <row r="27">
@@ -1021,16 +1021,16 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.3563451150321967</v>
+        <v>0.3503019397465578</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>0.3564803096228731</v>
+        <v>0.3503935102975514</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.6284754048827771</v>
+        <v>0.6238584975789174</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.3461731503989423</v>
+        <v>0.3413235615114343</v>
       </c>
     </row>
     <row r="29">
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>0.3669325647612571</v>
+        <v/>
       </c>
       <c r="E29" s="1" t="n">
-        <v>0.3663206665327311</v>
+        <v/>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6963470914156765</v>
+        <v/>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.3511115774936747</v>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1079,16 +1079,16 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>0.279143545828204</v>
+        <v/>
       </c>
       <c r="E30" s="1" t="n">
-        <v>0.2786879790877256</v>
+        <v/>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.6963470914156765</v>
+        <v/>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.2593096758197861</v>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1166,16 +1166,16 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>0.1626243201731267</v>
+        <v>0.1687993684210016</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>0.1627800258435922</v>
+        <v>0.169042671560123</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.6904054666112024</v>
+        <v>0.6879498821170513</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.1969544528672194</v>
+        <v>0.2019418899934239</v>
       </c>
     </row>
     <row r="34">
@@ -1195,16 +1195,16 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>0.1999446882105644</v>
+        <v>0.2093115439521635</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>0.1990099618688344</v>
+        <v>0.2077763990680182</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.6904054666112024</v>
+        <v>0.6879498821170513</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.2046038823179127</v>
+        <v>0.212622354765796</v>
       </c>
     </row>
   </sheetData>
@@ -1282,16 +1282,16 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.4025638759884939</v>
+        <v/>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.4026005690798778</v>
+        <v/>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.6767603191312457</v>
+        <v/>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.3976371924804952</v>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -1311,16 +1311,16 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.2637911557068653</v>
+        <v/>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.2882269899047988</v>
+        <v/>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.6767603191312457</v>
+        <v/>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.249120011239413</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1398,16 +1398,16 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.2770850836677314</v>
+        <v>0.2805402632693823</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>0.2828948406416403</v>
+        <v>0.2838798868954365</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6944222741672884</v>
+        <v>0.6948511663128721</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.2439762028463032</v>
+        <v>0.2443427104021553</v>
       </c>
     </row>
     <row r="9">
@@ -1427,16 +1427,16 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.4088046612319854</v>
+        <v>0.4088045639901903</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>0.4088049043929502</v>
+        <v>0.4088048895412726</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.6944213395824155</v>
+        <v>0.6948511920633094</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.4088048383026311</v>
+        <v>0.4088046934436602</v>
       </c>
     </row>
     <row r="11">
@@ -1456,16 +1456,16 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.3155247554601252</v>
+        <v/>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0.3154459504258927</v>
+        <v/>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.6982631321230246</v>
+        <v/>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.3070479089818113</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1485,16 +1485,16 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.2814671838726204</v>
+        <v/>
       </c>
       <c r="E12" s="1" t="n">
-        <v>0.284386291687972</v>
+        <v/>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.6982631321230246</v>
+        <v/>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.245412910407159</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1572,16 +1572,16 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.2116817275415259</v>
+        <v>0.212763286877736</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>0.2130596260346273</v>
+        <v>0.2142888793615748</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.7046451248351578</v>
+        <v>0.7039387158140619</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.2044736868875028</v>
+        <v>0.2055164070696674</v>
       </c>
     </row>
     <row r="16">
@@ -1601,16 +1601,16 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.2267894851397113</v>
+        <v>0.2316893047465645</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>0.2279254816284929</v>
+        <v>0.2321151252376342</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.7046451248351578</v>
+        <v>0.7039377736238388</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.2312835411140565</v>
+        <v>0.2339533122557886</v>
       </c>
     </row>
     <row r="19">
@@ -1674,16 +1674,16 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.2421890060911559</v>
+        <v/>
       </c>
       <c r="E22" s="1" t="n">
-        <v>0.2420007968429767</v>
+        <v/>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.6904863634584841</v>
+        <v/>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.2834645195181634</v>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.1955434689238541</v>
+        <v/>
       </c>
       <c r="E23" s="1" t="n">
-        <v>0.2417315802987232</v>
+        <v/>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.6904863634584841</v>
+        <v/>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.2416726221908596</v>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.2644893620825475</v>
+        <v>0.2683105166197954</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>0.2706485555216696</v>
+        <v>0.271995570886208</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.6972733532260277</v>
+        <v>0.6992207782887911</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.2739194485392034</v>
+        <v>0.2744356413844317</v>
       </c>
     </row>
     <row r="27">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.6002664910999002</v>
+        <v>0.6002664936410332</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>0.6002664910999002</v>
+        <v>0.6002664936410332</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.697270806752893</v>
+        <v>0.6992207782887911</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.6002659634403663</v>
+        <v>0.600265973485726</v>
       </c>
     </row>
     <row r="29">
@@ -1848,16 +1848,16 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>0.2416845045527448</v>
+        <v/>
       </c>
       <c r="E29" s="1" t="n">
-        <v>0.2406481496669978</v>
+        <v/>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.7291991454565866</v>
+        <v/>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.2512288804489629</v>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1877,16 +1877,16 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>0.1998965109398555</v>
+        <v/>
       </c>
       <c r="E30" s="1" t="n">
-        <v>0.1990644396969926</v>
+        <v/>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.7291991454565866</v>
+        <v/>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.2206155628521058</v>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1964,16 +1964,16 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>0.1262321402873332</v>
+        <v>0.1263646616642477</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>0.1297691549309277</v>
+        <v>0.1300199520758286</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.7349228880185197</v>
+        <v>0.7326260706988132</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.1972326646140375</v>
+        <v>0.198409464462993</v>
       </c>
     </row>
     <row r="34">
@@ -1993,16 +1993,16 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>0.2286983813391163</v>
+        <v>0.2355754720040678</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>0.2298005390446626</v>
+        <v>0.2345466998161674</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.7349228880185197</v>
+        <v>0.7326238722549597</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.2556983859511465</v>
+        <v>0.2580345561383483</v>
       </c>
     </row>
   </sheetData>
